--- a/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/gpt-4o-mini/heterogeneity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/gpt-4o-mini/heterogeneity.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K217"/>
+  <dimension ref="A1:K241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5662,19 +5662,19 @@
         <v>32</v>
       </c>
       <c r="G122" t="n">
-        <v>0.8769559433621934</v>
+        <v>0.9674479166666667</v>
       </c>
       <c r="H122" t="n">
-        <v>0.05785832115089543</v>
+        <v>0.1453946454811449</v>
       </c>
       <c r="I122" t="n">
-        <v>0.0102280028084668</v>
+        <v>0.0257023849419829</v>
       </c>
       <c r="J122" t="n">
-        <v>0.8188187944302074</v>
+        <v>0.9310887896825397</v>
       </c>
       <c r="K122" t="n">
-        <v>0.05813714893198596</v>
+        <v>0.03635912698412702</v>
       </c>
     </row>
     <row r="123">
@@ -5705,19 +5705,19 @@
         <v>32</v>
       </c>
       <c r="G123" t="n">
-        <v>0.3211422121372779</v>
+        <v>0.2238706452860865</v>
       </c>
       <c r="H123" t="n">
-        <v>0.195289340994499</v>
+        <v>0.2364969846172372</v>
       </c>
       <c r="I123" t="n">
-        <v>0.03452260432766557</v>
+        <v>0.04180715538825476</v>
       </c>
       <c r="J123" t="n">
-        <v>0.1830094011595559</v>
+        <v>0.0837915123071373</v>
       </c>
       <c r="K123" t="n">
-        <v>0.138132810977722</v>
+        <v>0.1400791329789492</v>
       </c>
     </row>
     <row r="124">
@@ -5748,19 +5748,19 @@
         <v>32</v>
       </c>
       <c r="G124" t="n">
-        <v>0.524374497030747</v>
+        <v>0.5574990981240981</v>
       </c>
       <c r="H124" t="n">
-        <v>0.144015597024612</v>
+        <v>0.2111989942997537</v>
       </c>
       <c r="I124" t="n">
-        <v>0.02545860131318307</v>
+        <v>0.0373350602622837</v>
       </c>
       <c r="J124" t="n">
-        <v>0.4596526617386592</v>
+        <v>0.504222250424696</v>
       </c>
       <c r="K124" t="n">
-        <v>0.06472183529208786</v>
+        <v>0.05327684769940211</v>
       </c>
     </row>
     <row r="125">
@@ -5791,19 +5791,19 @@
         <v>32</v>
       </c>
       <c r="G125" t="n">
-        <v>0.8657591540404042</v>
+        <v>0.996875</v>
       </c>
       <c r="H125" t="n">
-        <v>0.07236773892105967</v>
+        <v>0.01767766952966368</v>
       </c>
       <c r="I125" t="n">
-        <v>0.01279292973255474</v>
+        <v>0.003124999999999998</v>
       </c>
       <c r="J125" t="n">
-        <v>0.8188187944302074</v>
+        <v>0.9310887896825397</v>
       </c>
       <c r="K125" t="n">
-        <v>0.04694035961019671</v>
+        <v>0.06578621031746024</v>
       </c>
     </row>
     <row r="126">
@@ -5834,19 +5834,19 @@
         <v>32</v>
       </c>
       <c r="G126" t="n">
-        <v>0.3146724457686986</v>
+        <v>0.2309155341186591</v>
       </c>
       <c r="H126" t="n">
-        <v>0.2515788813387113</v>
+        <v>0.2799652145962827</v>
       </c>
       <c r="I126" t="n">
-        <v>0.04447328324948212</v>
+        <v>0.04949132543434461</v>
       </c>
       <c r="J126" t="n">
-        <v>0.1830094011595559</v>
+        <v>0.0837915123071373</v>
       </c>
       <c r="K126" t="n">
-        <v>0.1316630446091427</v>
+        <v>0.1471240218115218</v>
       </c>
     </row>
     <row r="127">
@@ -5877,19 +5877,19 @@
         <v>32</v>
       </c>
       <c r="G127" t="n">
-        <v>0.5345894097732333</v>
+        <v>0.5043542387050515</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1467193586260198</v>
+        <v>0.2095635487344234</v>
       </c>
       <c r="I127" t="n">
-        <v>0.02593656335394989</v>
+        <v>0.03704595159990708</v>
       </c>
       <c r="J127" t="n">
-        <v>0.4596526617386592</v>
+        <v>0.504222250424696</v>
       </c>
       <c r="K127" t="n">
-        <v>0.07493674803457417</v>
+        <v>0.0001319882803554329</v>
       </c>
     </row>
     <row r="128">
@@ -5920,19 +5920,19 @@
         <v>32</v>
       </c>
       <c r="G128" t="n">
-        <v>0.8787868004579962</v>
+        <v>0.9986979166666667</v>
       </c>
       <c r="H128" t="n">
-        <v>0.07333511798695803</v>
+        <v>0.007365695637359863</v>
       </c>
       <c r="I128" t="n">
-        <v>0.01296393980692339</v>
+        <v>0.001302083333333332</v>
       </c>
       <c r="J128" t="n">
-        <v>0.8269659801249475</v>
+        <v>0.9080007735142805</v>
       </c>
       <c r="K128" t="n">
-        <v>0.05182082033304869</v>
+        <v>0.09069714315238619</v>
       </c>
     </row>
     <row r="129">
@@ -5963,19 +5963,19 @@
         <v>32</v>
       </c>
       <c r="G129" t="n">
-        <v>0.4672090079874396</v>
+        <v>0.4140181935720219</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2053759460907271</v>
+        <v>0.3354923699876741</v>
       </c>
       <c r="I129" t="n">
-        <v>0.03630568104333899</v>
+        <v>0.05930723246365762</v>
       </c>
       <c r="J129" t="n">
-        <v>0.14071079687856</v>
+        <v>0.06137352231102231</v>
       </c>
       <c r="K129" t="n">
-        <v>0.3264982111088796</v>
+        <v>0.3526446712609996</v>
       </c>
     </row>
     <row r="130">
@@ -6006,19 +6006,19 @@
         <v>32</v>
       </c>
       <c r="G130" t="n">
-        <v>0.7093175845893237</v>
+        <v>0.7846504884004885</v>
       </c>
       <c r="H130" t="n">
-        <v>0.08896178340704643</v>
+        <v>0.1063603066864399</v>
       </c>
       <c r="I130" t="n">
-        <v>0.01572637007839285</v>
+        <v>0.01880202352676563</v>
       </c>
       <c r="J130" t="n">
-        <v>0.4445382507163197</v>
+        <v>0.4573478136500582</v>
       </c>
       <c r="K130" t="n">
-        <v>0.264779333873004</v>
+        <v>0.3273026747504302</v>
       </c>
     </row>
     <row r="131">
@@ -6049,19 +6049,19 @@
         <v>32</v>
       </c>
       <c r="G131" t="n">
-        <v>0.8787868004579962</v>
+        <v>0.9986979166666667</v>
       </c>
       <c r="H131" t="n">
-        <v>0.07333511798695803</v>
+        <v>0.007365695637359863</v>
       </c>
       <c r="I131" t="n">
-        <v>0.01296393980692339</v>
+        <v>0.001302083333333332</v>
       </c>
       <c r="J131" t="n">
-        <v>0.8269659801249475</v>
+        <v>0.9080007735142805</v>
       </c>
       <c r="K131" t="n">
-        <v>0.05182082033304869</v>
+        <v>0.09069714315238619</v>
       </c>
     </row>
     <row r="132">
@@ -6092,19 +6092,19 @@
         <v>32</v>
       </c>
       <c r="G132" t="n">
-        <v>0.4672090079874396</v>
+        <v>0.4140181935720219</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2053759460907271</v>
+        <v>0.3354923699876741</v>
       </c>
       <c r="I132" t="n">
-        <v>0.03630568104333899</v>
+        <v>0.05930723246365762</v>
       </c>
       <c r="J132" t="n">
-        <v>0.14071079687856</v>
+        <v>0.06137352231102231</v>
       </c>
       <c r="K132" t="n">
-        <v>0.3264982111088796</v>
+        <v>0.3526446712609996</v>
       </c>
     </row>
     <row r="133">
@@ -6135,19 +6135,19 @@
         <v>32</v>
       </c>
       <c r="G133" t="n">
-        <v>0.7093175845893237</v>
+        <v>0.7846504884004885</v>
       </c>
       <c r="H133" t="n">
-        <v>0.08896178340704643</v>
+        <v>0.1063603066864399</v>
       </c>
       <c r="I133" t="n">
-        <v>0.01572637007839285</v>
+        <v>0.01880202352676563</v>
       </c>
       <c r="J133" t="n">
-        <v>0.4445382507163197</v>
+        <v>0.4573478136500582</v>
       </c>
       <c r="K133" t="n">
-        <v>0.264779333873004</v>
+        <v>0.3273026747504302</v>
       </c>
     </row>
     <row r="134">
@@ -6178,19 +6178,19 @@
         <v>32</v>
       </c>
       <c r="G134" t="n">
-        <v>0.8760258838383839</v>
+        <v>0.9848214285714286</v>
       </c>
       <c r="H134" t="n">
-        <v>0.08821319520988255</v>
+        <v>0.04867399038866135</v>
       </c>
       <c r="I134" t="n">
-        <v>0.01559403713076015</v>
+        <v>0.008604427167807818</v>
       </c>
       <c r="J134" t="n">
-        <v>0.8288222870106368</v>
+        <v>0.9798239087301587</v>
       </c>
       <c r="K134" t="n">
-        <v>0.04720359682774711</v>
+        <v>0.004997519841269948</v>
       </c>
     </row>
     <row r="135">
@@ -6221,19 +6221,19 @@
         <v>32</v>
       </c>
       <c r="G135" t="n">
-        <v>0.4470503429372915</v>
+        <v>0.2953340139231683</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1437530976213926</v>
+        <v>0.1981606907445154</v>
       </c>
       <c r="I135" t="n">
-        <v>0.02541219753616462</v>
+        <v>0.03503019204751429</v>
       </c>
       <c r="J135" t="n">
-        <v>0.2088666541791542</v>
+        <v>0.08279085493866672</v>
       </c>
       <c r="K135" t="n">
-        <v>0.2381836887581373</v>
+        <v>0.2125431589845016</v>
       </c>
     </row>
     <row r="136">
@@ -6264,19 +6264,19 @@
         <v>32</v>
       </c>
       <c r="G136" t="n">
-        <v>0.567335049550123</v>
+        <v>0.5641105467996915</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1550863747163262</v>
+        <v>0.1823964193675573</v>
       </c>
       <c r="I136" t="n">
-        <v>0.02741565680788805</v>
+        <v>0.03224343624973627</v>
       </c>
       <c r="J136" t="n">
-        <v>0.4286665402833881</v>
+        <v>0.4173844401544336</v>
       </c>
       <c r="K136" t="n">
-        <v>0.1386685092667349</v>
+        <v>0.1467261066452579</v>
       </c>
     </row>
     <row r="137">
@@ -6307,19 +6307,19 @@
         <v>32</v>
       </c>
       <c r="G137" t="n">
-        <v>0.8760258838383839</v>
+        <v>0.9848214285714286</v>
       </c>
       <c r="H137" t="n">
-        <v>0.08821319520988255</v>
+        <v>0.04867399038866135</v>
       </c>
       <c r="I137" t="n">
-        <v>0.01559403713076015</v>
+        <v>0.008604427167807818</v>
       </c>
       <c r="J137" t="n">
-        <v>0.8288222870106368</v>
+        <v>0.9798239087301587</v>
       </c>
       <c r="K137" t="n">
-        <v>0.04720359682774711</v>
+        <v>0.004997519841269948</v>
       </c>
     </row>
     <row r="138">
@@ -6350,19 +6350,19 @@
         <v>32</v>
       </c>
       <c r="G138" t="n">
-        <v>0.4470503429372915</v>
+        <v>0.2953340139231683</v>
       </c>
       <c r="H138" t="n">
-        <v>0.1437530976213926</v>
+        <v>0.1981606907445154</v>
       </c>
       <c r="I138" t="n">
-        <v>0.02541219753616462</v>
+        <v>0.03503019204751429</v>
       </c>
       <c r="J138" t="n">
-        <v>0.2088666541791542</v>
+        <v>0.08279085493866672</v>
       </c>
       <c r="K138" t="n">
-        <v>0.2381836887581373</v>
+        <v>0.2125431589845016</v>
       </c>
     </row>
     <row r="139">
@@ -6393,19 +6393,19 @@
         <v>32</v>
       </c>
       <c r="G139" t="n">
-        <v>0.567335049550123</v>
+        <v>0.5641105467996915</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1550863747163262</v>
+        <v>0.1823964193675573</v>
       </c>
       <c r="I139" t="n">
-        <v>0.02741565680788805</v>
+        <v>0.03224343624973627</v>
       </c>
       <c r="J139" t="n">
-        <v>0.4286665402833881</v>
+        <v>0.4173844401544336</v>
       </c>
       <c r="K139" t="n">
-        <v>0.1386685092667349</v>
+        <v>0.1467261066452579</v>
       </c>
     </row>
     <row r="140">
@@ -6436,19 +6436,19 @@
         <v>32</v>
       </c>
       <c r="G140" t="n">
-        <v>0.8704223426030491</v>
+        <v>0.9942336309523809</v>
       </c>
       <c r="H140" t="n">
-        <v>0.06003386175201832</v>
+        <v>0.02607695929769964</v>
       </c>
       <c r="I140" t="n">
-        <v>0.01061258768641696</v>
+        <v>0.004609798688032252</v>
       </c>
       <c r="J140" t="n">
-        <v>0.8286928069976344</v>
+        <v>0.9753336940836941</v>
       </c>
       <c r="K140" t="n">
-        <v>0.0417295356054147</v>
+        <v>0.01889993686868685</v>
       </c>
     </row>
     <row r="141">
@@ -6479,19 +6479,19 @@
         <v>32</v>
       </c>
       <c r="G141" t="n">
-        <v>0.4287275972548637</v>
+        <v>0.3600433629891351</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1939950481055751</v>
+        <v>0.2724109898947056</v>
       </c>
       <c r="I141" t="n">
-        <v>0.03429380350801567</v>
+        <v>0.04815591455607159</v>
       </c>
       <c r="J141" t="n">
-        <v>0.18428646006771</v>
+        <v>0.07645507270507271</v>
       </c>
       <c r="K141" t="n">
-        <v>0.2444411371871537</v>
+        <v>0.2835882902840624</v>
       </c>
     </row>
     <row r="142">
@@ -6522,19 +6522,19 @@
         <v>32</v>
       </c>
       <c r="G142" t="n">
-        <v>0.6142219630770621</v>
+        <v>0.6734839292651793</v>
       </c>
       <c r="H142" t="n">
-        <v>0.1738002260903071</v>
+        <v>0.2045041206045156</v>
       </c>
       <c r="I142" t="n">
-        <v>0.03072382961005282</v>
+        <v>0.03615156261501112</v>
       </c>
       <c r="J142" t="n">
-        <v>0.4312703084507941</v>
+        <v>0.4406110729548229</v>
       </c>
       <c r="K142" t="n">
-        <v>0.182951654626268</v>
+        <v>0.2328728563103564</v>
       </c>
     </row>
     <row r="143">
@@ -6565,19 +6565,19 @@
         <v>32</v>
       </c>
       <c r="G143" t="n">
-        <v>0.8704223426030491</v>
+        <v>0.9942336309523809</v>
       </c>
       <c r="H143" t="n">
-        <v>0.06003386175201832</v>
+        <v>0.02607695929769964</v>
       </c>
       <c r="I143" t="n">
-        <v>0.01061258768641696</v>
+        <v>0.004609798688032252</v>
       </c>
       <c r="J143" t="n">
-        <v>0.8286928069976344</v>
+        <v>0.9753336940836941</v>
       </c>
       <c r="K143" t="n">
-        <v>0.0417295356054147</v>
+        <v>0.01889993686868685</v>
       </c>
     </row>
     <row r="144">
@@ -6608,19 +6608,19 @@
         <v>32</v>
       </c>
       <c r="G144" t="n">
-        <v>0.4287275972548637</v>
+        <v>0.3600433629891351</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1939950481055751</v>
+        <v>0.2724109898947056</v>
       </c>
       <c r="I144" t="n">
-        <v>0.03429380350801567</v>
+        <v>0.04815591455607159</v>
       </c>
       <c r="J144" t="n">
-        <v>0.18428646006771</v>
+        <v>0.07645507270507271</v>
       </c>
       <c r="K144" t="n">
-        <v>0.2444411371871537</v>
+        <v>0.2835882902840624</v>
       </c>
     </row>
     <row r="145">
@@ -6651,19 +6651,19 @@
         <v>32</v>
       </c>
       <c r="G145" t="n">
-        <v>0.6142219630770621</v>
+        <v>0.6734839292651793</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1738002260903071</v>
+        <v>0.2045041206045156</v>
       </c>
       <c r="I145" t="n">
-        <v>0.03072382961005282</v>
+        <v>0.03615156261501112</v>
       </c>
       <c r="J145" t="n">
-        <v>0.4312703084507941</v>
+        <v>0.4406110729548229</v>
       </c>
       <c r="K145" t="n">
-        <v>0.182951654626268</v>
+        <v>0.2328728563103564</v>
       </c>
     </row>
     <row r="146">
@@ -9760,6 +9760,1038 @@
       </c>
       <c r="K217" t="n">
         <v>1.56985294117647</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>10</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>32</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0.1767766952966369</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0.03255208333333333</v>
+      </c>
+      <c r="K218" t="n">
+        <v>-0.001302083333333329</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>10</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>32</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0.1927083333333333</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0.2928642846905574</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0.05177158041801017</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0.02708333333333333</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0.165625</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>10</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>StartLowAndChangesToHigh</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>32</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0.140625</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0.2905604983919983</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0.05136432468948123</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0.09142992424242424</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0.04919507575757576</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>8</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>32</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0.03255208333333333</v>
+      </c>
+      <c r="K221" t="n">
+        <v>-0.03255208333333333</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>8</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>32</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0.1608072916666667</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.2807696702332613</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0.04963353444336244</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0.02708333333333333</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0.1337239583333333</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>8</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>StartLowAndChangesToHigh</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>32</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0.171875</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0.3265008768451398</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0.05771774602013804</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0.09142992424242424</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0.08044507575757576</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>10</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>32</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0.5010319541569541</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0.4636889321280916</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0.08196939706723058</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0.0734375</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0.4275944541569541</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>10</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>32</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0.5549174783549784</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.3984873126910349</v>
+      </c>
+      <c r="I225" t="n">
+        <v>0.07044327025515874</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0.1052083333333333</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0.4497091450216451</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>10</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>StartLowAndChangesToHigh</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>32</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0.7278711484593837</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.3242595566943017</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0.05732153285077112</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0.090625</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0.6372461484593838</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>10</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>32</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0.5010319541569541</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0.4636889321280916</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0.08196939706723058</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0.0734375</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0.4275944541569541</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>10</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>32</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0.5549174783549784</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0.3984873126910349</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0.07044327025515874</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0.1052083333333333</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0.4497091450216451</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>10</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>StartLowAndChangesToHigh</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>32</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0.7278711484593837</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0.3242595566943017</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0.05732153285077112</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0.090625</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0.6372461484593838</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>10</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>32</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="K230" t="n">
+        <v>-0.03125</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>10</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>32</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0.3385416666666666</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0.3477639143777991</v>
+      </c>
+      <c r="I231" t="n">
+        <v>0.0614765555271299</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0.05458447802197802</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0.2839571886446886</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>10</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>StartLowAndChangesToHigh</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>32</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0.3463541666666666</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0.3845756954122194</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0.06798402052637813</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0.1402310924369748</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0.2061230742296918</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>10</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>32</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="K233" t="n">
+        <v>-0.03125</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>10</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>32</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0.3385416666666666</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.3477639143777991</v>
+      </c>
+      <c r="I234" t="n">
+        <v>0.0614765555271299</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0.05458447802197802</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0.2839571886446886</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>10</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>StartLowAndChangesToHigh</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>32</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.3463541666666666</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0.3845756954122194</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0.06798402052637813</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0.1402310924369748</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0.2061230742296918</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>10</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>32</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0.1796875</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.3365831998897578</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0.05950006576887874</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0.007612179487179484</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0.1720753205128205</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>10</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>32</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0.4171874999999999</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0.4142939836979477</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0.07323752131940195</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0.07254464285714285</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0.3446428571428571</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>10</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>StartLowAndChangesToHigh</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>32</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0.4172281711344211</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.440570749941942</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0.07788264121909748</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0.1561710858585859</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0.2610570852758353</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>10</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>32</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0.1796875</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.3365831998897578</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0.05950006576887874</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0.007612179487179484</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0.1720753205128205</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>10</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>32</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0.4171874999999999</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0.4142939836979477</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0.07323752131940195</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0.07254464285714285</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0.3446428571428571</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>10</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>StartLowAndChangesToHigh</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>32</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.4172281711344211</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0.440570749941942</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0.07788264121909748</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0.1561710858585859</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0.2610570852758353</v>
       </c>
     </row>
   </sheetData>
@@ -9773,7 +10805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13301,19 +14333,19 @@
         <v>48</v>
       </c>
       <c r="G82" t="n">
-        <v>0.5862464989932096</v>
+        <v>0.5817001863876864</v>
       </c>
       <c r="H82" t="n">
-        <v>0.2599880312008225</v>
+        <v>0.3765249169252143</v>
       </c>
       <c r="I82" t="n">
-        <v>0.03752603994996892</v>
+        <v>0.0543466905358435</v>
       </c>
       <c r="J82" t="n">
-        <v>0.4982157935722514</v>
+        <v>0.5136249800923715</v>
       </c>
       <c r="K82" t="n">
-        <v>0.0880307054209582</v>
+        <v>0.06807520629531494</v>
       </c>
     </row>
     <row r="83">
@@ -13344,19 +14376,19 @@
         <v>48</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5620686026936027</v>
+        <v>0.5841782536635477</v>
       </c>
       <c r="H83" t="n">
-        <v>0.2843391862733435</v>
+        <v>0.3568817025147624</v>
       </c>
       <c r="I83" t="n">
-        <v>0.04104082643401851</v>
+        <v>0.05151143675393751</v>
       </c>
       <c r="J83" t="n">
-        <v>0.4761047779800303</v>
+        <v>0.499110054850544</v>
       </c>
       <c r="K83" t="n">
-        <v>0.08596382471357239</v>
+        <v>0.0850681988130037</v>
       </c>
     </row>
     <row r="84">
@@ -13387,19 +14419,19 @@
         <v>48</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5677287683721507</v>
+        <v>0.5853684793627711</v>
       </c>
       <c r="H84" t="n">
-        <v>0.2892062964263516</v>
+        <v>0.3709861667245872</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0417433332732722</v>
+        <v>0.05354724080601696</v>
       </c>
       <c r="J84" t="n">
-        <v>0.4982157935722514</v>
+        <v>0.5136249800923715</v>
       </c>
       <c r="K84" t="n">
-        <v>0.06951297479989932</v>
+        <v>0.07174349927039969</v>
       </c>
     </row>
     <row r="85">
@@ -13430,19 +14462,19 @@
         <v>48</v>
       </c>
       <c r="G85" t="n">
-        <v>0.5756185713494065</v>
+        <v>0.5693947025197025</v>
       </c>
       <c r="H85" t="n">
-        <v>0.2837549423254207</v>
+        <v>0.3850732089139043</v>
       </c>
       <c r="I85" t="n">
-        <v>0.04095649808386709</v>
+        <v>0.05558053020603892</v>
       </c>
       <c r="J85" t="n">
-        <v>0.4761047779800303</v>
+        <v>0.499110054850544</v>
       </c>
       <c r="K85" t="n">
-        <v>0.09951379336937621</v>
+        <v>0.07028464766915848</v>
       </c>
     </row>
     <row r="86">
@@ -13473,19 +14505,19 @@
         <v>48</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6746614014596751</v>
+        <v>0.7233010657051576</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1928325308905648</v>
+        <v>0.3105497129776382</v>
       </c>
       <c r="I86" t="n">
-        <v>0.02783297840454611</v>
+        <v>0.04482399009610011</v>
       </c>
       <c r="J86" t="n">
-        <v>0.464800525657892</v>
+        <v>0.480590899284953</v>
       </c>
       <c r="K86" t="n">
-        <v>0.2098608758017831</v>
+        <v>0.2427101664202046</v>
       </c>
     </row>
     <row r="87">
@@ -13516,19 +14548,19 @@
         <v>48</v>
       </c>
       <c r="G87" t="n">
-        <v>0.6955475272301644</v>
+        <v>0.7416100000542935</v>
       </c>
       <c r="H87" t="n">
-        <v>0.2396790010014723</v>
+        <v>0.3229245979034863</v>
       </c>
       <c r="I87" t="n">
-        <v>0.03459468393682515</v>
+        <v>0.04661015088188238</v>
       </c>
       <c r="J87" t="n">
-        <v>0.4766761594886595</v>
+        <v>0.4705571736986211</v>
       </c>
       <c r="K87" t="n">
-        <v>0.218871367741505</v>
+        <v>0.2710528263556723</v>
       </c>
     </row>
     <row r="88">
@@ -13559,19 +14591,19 @@
         <v>48</v>
       </c>
       <c r="G88" t="n">
-        <v>0.6746614014596751</v>
+        <v>0.7233010657051576</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1928325308905648</v>
+        <v>0.3105497129776382</v>
       </c>
       <c r="I88" t="n">
-        <v>0.02783297840454611</v>
+        <v>0.04482399009610011</v>
       </c>
       <c r="J88" t="n">
-        <v>0.464800525657892</v>
+        <v>0.480590899284953</v>
       </c>
       <c r="K88" t="n">
-        <v>0.2098608758017831</v>
+        <v>0.2427101664202046</v>
       </c>
     </row>
     <row r="89">
@@ -13602,19 +14634,19 @@
         <v>48</v>
       </c>
       <c r="G89" t="n">
-        <v>0.6955475272301644</v>
+        <v>0.7416100000542935</v>
       </c>
       <c r="H89" t="n">
-        <v>0.2396790010014723</v>
+        <v>0.3229245979034863</v>
       </c>
       <c r="I89" t="n">
-        <v>0.03459468393682515</v>
+        <v>0.04661015088188238</v>
       </c>
       <c r="J89" t="n">
-        <v>0.4766761594886595</v>
+        <v>0.4705571736986211</v>
       </c>
       <c r="K89" t="n">
-        <v>0.218871367741505</v>
+        <v>0.2710528263556723</v>
       </c>
     </row>
     <row r="90">
@@ -13645,19 +14677,19 @@
         <v>48</v>
       </c>
       <c r="G90" t="n">
-        <v>0.6508541788413112</v>
+        <v>0.6392533681596181</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1911711731215662</v>
+        <v>0.2995920749884532</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0275931820657582</v>
+        <v>0.04324239128541551</v>
       </c>
       <c r="J90" t="n">
-        <v>0.4854256150451803</v>
+        <v>0.5008675619192681</v>
       </c>
       <c r="K90" t="n">
-        <v>0.165428563796131</v>
+        <v>0.13838580624035</v>
       </c>
     </row>
     <row r="91">
@@ -13688,19 +14720,19 @@
         <v>48</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6094200053758877</v>
+        <v>0.5902572913699075</v>
       </c>
       <c r="H91" t="n">
-        <v>0.2527381839441201</v>
+        <v>0.3505419970615332</v>
       </c>
       <c r="I91" t="n">
-        <v>0.03647961463365873</v>
+        <v>0.0505963790914363</v>
       </c>
       <c r="J91" t="n">
-        <v>0.4921447059369391</v>
+        <v>0.4857985739629047</v>
       </c>
       <c r="K91" t="n">
-        <v>0.1172752994389486</v>
+        <v>0.1044587174070028</v>
       </c>
     </row>
     <row r="92">
@@ -13731,19 +14763,19 @@
         <v>48</v>
       </c>
       <c r="G92" t="n">
-        <v>0.6508541788413112</v>
+        <v>0.6392533681596181</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1911711731215662</v>
+        <v>0.2995920749884532</v>
       </c>
       <c r="I92" t="n">
-        <v>0.0275931820657582</v>
+        <v>0.04324239128541551</v>
       </c>
       <c r="J92" t="n">
-        <v>0.4854256150451803</v>
+        <v>0.5008675619192681</v>
       </c>
       <c r="K92" t="n">
-        <v>0.165428563796131</v>
+        <v>0.13838580624035</v>
       </c>
     </row>
     <row r="93">
@@ -13774,19 +14806,19 @@
         <v>48</v>
       </c>
       <c r="G93" t="n">
-        <v>0.6094200053758877</v>
+        <v>0.5902572913699075</v>
       </c>
       <c r="H93" t="n">
-        <v>0.2527381839441201</v>
+        <v>0.3505419970615332</v>
       </c>
       <c r="I93" t="n">
-        <v>0.03647961463365873</v>
+        <v>0.0505963790914363</v>
       </c>
       <c r="J93" t="n">
-        <v>0.4921447059369391</v>
+        <v>0.4857985739629047</v>
       </c>
       <c r="K93" t="n">
-        <v>0.1172752994389486</v>
+        <v>0.1044587174070028</v>
       </c>
     </row>
     <row r="94">
@@ -13817,19 +14849,19 @@
         <v>48</v>
       </c>
       <c r="G94" t="n">
-        <v>0.6489791146560648</v>
+        <v>0.6865798345853493</v>
       </c>
       <c r="H94" t="n">
-        <v>0.2213665160194002</v>
+        <v>0.3042328829593419</v>
       </c>
       <c r="I94" t="n">
-        <v>0.03195150440334259</v>
+        <v>0.04391223421822799</v>
       </c>
       <c r="J94" t="n">
-        <v>0.4852671390305787</v>
+        <v>0.4862130924630925</v>
       </c>
       <c r="K94" t="n">
-        <v>0.1637119756254861</v>
+        <v>0.2003667421222569</v>
       </c>
     </row>
     <row r="95">
@@ -13860,19 +14892,19 @@
         <v>48</v>
       </c>
       <c r="G95" t="n">
-        <v>0.6266021539672519</v>
+        <v>0.6652607808857809</v>
       </c>
       <c r="H95" t="n">
-        <v>0.2546499824035546</v>
+        <v>0.3480133467314255</v>
       </c>
       <c r="I95" t="n">
-        <v>0.03675555897245644</v>
+        <v>0.05023139985424278</v>
       </c>
       <c r="J95" t="n">
-        <v>0.4775659113135136</v>
+        <v>0.5087201340326341</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1490362426537383</v>
+        <v>0.1565406468531468</v>
       </c>
     </row>
     <row r="96">
@@ -13903,19 +14935,19 @@
         <v>48</v>
       </c>
       <c r="G96" t="n">
-        <v>0.6489791146560648</v>
+        <v>0.6865798345853493</v>
       </c>
       <c r="H96" t="n">
-        <v>0.2213665160194002</v>
+        <v>0.3042328829593419</v>
       </c>
       <c r="I96" t="n">
-        <v>0.03195150440334259</v>
+        <v>0.04391223421822799</v>
       </c>
       <c r="J96" t="n">
-        <v>0.4852671390305787</v>
+        <v>0.4862130924630925</v>
       </c>
       <c r="K96" t="n">
-        <v>0.1637119756254861</v>
+        <v>0.2003667421222569</v>
       </c>
     </row>
     <row r="97">
@@ -13946,19 +14978,19 @@
         <v>48</v>
       </c>
       <c r="G97" t="n">
-        <v>0.6266021539672519</v>
+        <v>0.6652607808857809</v>
       </c>
       <c r="H97" t="n">
-        <v>0.2546499824035546</v>
+        <v>0.3480133467314255</v>
       </c>
       <c r="I97" t="n">
-        <v>0.03675555897245644</v>
+        <v>0.05023139985424278</v>
       </c>
       <c r="J97" t="n">
-        <v>0.4775659113135136</v>
+        <v>0.5087201340326341</v>
       </c>
       <c r="K97" t="n">
-        <v>0.1490362426537383</v>
+        <v>0.1565406468531468</v>
       </c>
     </row>
     <row r="98">
@@ -16023,6 +17055,694 @@
       </c>
       <c r="K145" t="n">
         <v>1.117647058823529</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Obesity</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>48</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.1076388888888889</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0.2436900701214716</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.0351736318958676</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.05765467171717172</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0.04998421717171716</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>48</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.1354166666666667</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0.2869424905931525</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.04141658104647457</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0.04305555555555555</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0.09236111111111112</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>8</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Obesity</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>48</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0.08637152777777778</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0.2265929616284556</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0.03270587684816585</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0.05765467171717172</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0.02871685606060605</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>GRPO_LA0</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>8</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>48</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0.1354166666666667</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0.2869424905931525</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0.04141658104647457</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0.04305555555555555</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0.09236111111111112</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Obesity</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>48</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.5461115681703917</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0.4203785072367995</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0.06067641107867481</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0.4975004570592806</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>48</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.6431021524771525</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0.3917946805236284</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0.05655069106684508</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0.1309027777777778</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0.5121993746993747</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Obesity</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>48</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.5461115681703917</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0.4203785072367995</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0.06067641107867481</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.0486111111111111</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0.4975004570592806</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>GRPO_LA5</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>48</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.6431021524771525</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0.3917946805236284</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0.05655069106684508</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0.1309027777777778</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0.5121993746993747</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Obesity</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>48</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0.3374450893660678</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0.04870600329555414</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.06026785714285714</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0.1619543650793651</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>48</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.234375</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0.3415028365215227</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0.04929168864868048</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0.0904425231631114</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0.1439324768368886</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Obesity</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>48</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.3374450893660678</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.04870600329555414</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0.06026785714285714</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0.1619543650793651</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PTO_LA0</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>48</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0.234375</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0.3415028365215227</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0.04929168864868048</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0.0904425231631114</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0.1439324768368886</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Obesity</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>48</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.2849492521367521</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.3734680729129244</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.05390547310750192</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.08229166666666667</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0.2026575854700854</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>final</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>48</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.3911195286195286</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0.4430903101067879</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0.06395457745386719</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.07526027213527213</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0.3158592564842564</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Obesity</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>48</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0.2849492521367521</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0.3734680729129244</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0.05390547310750192</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.08229166666666667</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0.2026575854700854</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MIPROC</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>best</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Smoking</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>48</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0.3911195286195286</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.4430903101067879</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0.06395457745386719</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.07526027213527213</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0.3158592564842564</v>
       </c>
     </row>
   </sheetData>

--- a/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/gpt-4o-mini/heterogeneity.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/heterogeneity/tables/gpt-4o-mini/heterogeneity.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K241"/>
+  <dimension ref="A1:K217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9760,1038 +9760,6 @@
       </c>
       <c r="K217" t="n">
         <v>1.56985294117647</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>GRPO_LA0</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>10</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F218" t="n">
-        <v>32</v>
-      </c>
-      <c r="G218" t="n">
-        <v>0.03125</v>
-      </c>
-      <c r="H218" t="n">
-        <v>0.1767766952966369</v>
-      </c>
-      <c r="I218" t="n">
-        <v>0.03125</v>
-      </c>
-      <c r="J218" t="n">
-        <v>0.03255208333333333</v>
-      </c>
-      <c r="K218" t="n">
-        <v>-0.001302083333333329</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>GRPO_LA0</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>10</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F219" t="n">
-        <v>32</v>
-      </c>
-      <c r="G219" t="n">
-        <v>0.1927083333333333</v>
-      </c>
-      <c r="H219" t="n">
-        <v>0.2928642846905574</v>
-      </c>
-      <c r="I219" t="n">
-        <v>0.05177158041801017</v>
-      </c>
-      <c r="J219" t="n">
-        <v>0.02708333333333333</v>
-      </c>
-      <c r="K219" t="n">
-        <v>0.165625</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>GRPO_LA0</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>10</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>StartLowAndChangesToHigh</t>
-        </is>
-      </c>
-      <c r="F220" t="n">
-        <v>32</v>
-      </c>
-      <c r="G220" t="n">
-        <v>0.140625</v>
-      </c>
-      <c r="H220" t="n">
-        <v>0.2905604983919983</v>
-      </c>
-      <c r="I220" t="n">
-        <v>0.05136432468948123</v>
-      </c>
-      <c r="J220" t="n">
-        <v>0.09142992424242424</v>
-      </c>
-      <c r="K220" t="n">
-        <v>0.04919507575757576</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>GRPO_LA0</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>8</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F221" t="n">
-        <v>32</v>
-      </c>
-      <c r="G221" t="n">
-        <v>0</v>
-      </c>
-      <c r="H221" t="n">
-        <v>0</v>
-      </c>
-      <c r="I221" t="n">
-        <v>0</v>
-      </c>
-      <c r="J221" t="n">
-        <v>0.03255208333333333</v>
-      </c>
-      <c r="K221" t="n">
-        <v>-0.03255208333333333</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>GRPO_LA0</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>8</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F222" t="n">
-        <v>32</v>
-      </c>
-      <c r="G222" t="n">
-        <v>0.1608072916666667</v>
-      </c>
-      <c r="H222" t="n">
-        <v>0.2807696702332613</v>
-      </c>
-      <c r="I222" t="n">
-        <v>0.04963353444336244</v>
-      </c>
-      <c r="J222" t="n">
-        <v>0.02708333333333333</v>
-      </c>
-      <c r="K222" t="n">
-        <v>0.1337239583333333</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>GRPO_LA0</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>8</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>StartLowAndChangesToHigh</t>
-        </is>
-      </c>
-      <c r="F223" t="n">
-        <v>32</v>
-      </c>
-      <c r="G223" t="n">
-        <v>0.171875</v>
-      </c>
-      <c r="H223" t="n">
-        <v>0.3265008768451398</v>
-      </c>
-      <c r="I223" t="n">
-        <v>0.05771774602013804</v>
-      </c>
-      <c r="J223" t="n">
-        <v>0.09142992424242424</v>
-      </c>
-      <c r="K223" t="n">
-        <v>0.08044507575757576</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>GRPO_LA5</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>10</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F224" t="n">
-        <v>32</v>
-      </c>
-      <c r="G224" t="n">
-        <v>0.5010319541569541</v>
-      </c>
-      <c r="H224" t="n">
-        <v>0.4636889321280916</v>
-      </c>
-      <c r="I224" t="n">
-        <v>0.08196939706723058</v>
-      </c>
-      <c r="J224" t="n">
-        <v>0.0734375</v>
-      </c>
-      <c r="K224" t="n">
-        <v>0.4275944541569541</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>GRPO_LA5</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>10</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F225" t="n">
-        <v>32</v>
-      </c>
-      <c r="G225" t="n">
-        <v>0.5549174783549784</v>
-      </c>
-      <c r="H225" t="n">
-        <v>0.3984873126910349</v>
-      </c>
-      <c r="I225" t="n">
-        <v>0.07044327025515874</v>
-      </c>
-      <c r="J225" t="n">
-        <v>0.1052083333333333</v>
-      </c>
-      <c r="K225" t="n">
-        <v>0.4497091450216451</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>GRPO_LA5</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>10</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>StartLowAndChangesToHigh</t>
-        </is>
-      </c>
-      <c r="F226" t="n">
-        <v>32</v>
-      </c>
-      <c r="G226" t="n">
-        <v>0.7278711484593837</v>
-      </c>
-      <c r="H226" t="n">
-        <v>0.3242595566943017</v>
-      </c>
-      <c r="I226" t="n">
-        <v>0.05732153285077112</v>
-      </c>
-      <c r="J226" t="n">
-        <v>0.090625</v>
-      </c>
-      <c r="K226" t="n">
-        <v>0.6372461484593838</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>GRPO_LA5</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>10</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F227" t="n">
-        <v>32</v>
-      </c>
-      <c r="G227" t="n">
-        <v>0.5010319541569541</v>
-      </c>
-      <c r="H227" t="n">
-        <v>0.4636889321280916</v>
-      </c>
-      <c r="I227" t="n">
-        <v>0.08196939706723058</v>
-      </c>
-      <c r="J227" t="n">
-        <v>0.0734375</v>
-      </c>
-      <c r="K227" t="n">
-        <v>0.4275944541569541</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>GRPO_LA5</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>10</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F228" t="n">
-        <v>32</v>
-      </c>
-      <c r="G228" t="n">
-        <v>0.5549174783549784</v>
-      </c>
-      <c r="H228" t="n">
-        <v>0.3984873126910349</v>
-      </c>
-      <c r="I228" t="n">
-        <v>0.07044327025515874</v>
-      </c>
-      <c r="J228" t="n">
-        <v>0.1052083333333333</v>
-      </c>
-      <c r="K228" t="n">
-        <v>0.4497091450216451</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>GRPO_LA5</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>10</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>StartLowAndChangesToHigh</t>
-        </is>
-      </c>
-      <c r="F229" t="n">
-        <v>32</v>
-      </c>
-      <c r="G229" t="n">
-        <v>0.7278711484593837</v>
-      </c>
-      <c r="H229" t="n">
-        <v>0.3242595566943017</v>
-      </c>
-      <c r="I229" t="n">
-        <v>0.05732153285077112</v>
-      </c>
-      <c r="J229" t="n">
-        <v>0.090625</v>
-      </c>
-      <c r="K229" t="n">
-        <v>0.6372461484593838</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>PTO_LA0</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>10</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F230" t="n">
-        <v>32</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0</v>
-      </c>
-      <c r="H230" t="n">
-        <v>0</v>
-      </c>
-      <c r="I230" t="n">
-        <v>0</v>
-      </c>
-      <c r="J230" t="n">
-        <v>0.03125</v>
-      </c>
-      <c r="K230" t="n">
-        <v>-0.03125</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>PTO_LA0</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>10</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F231" t="n">
-        <v>32</v>
-      </c>
-      <c r="G231" t="n">
-        <v>0.3385416666666666</v>
-      </c>
-      <c r="H231" t="n">
-        <v>0.3477639143777991</v>
-      </c>
-      <c r="I231" t="n">
-        <v>0.0614765555271299</v>
-      </c>
-      <c r="J231" t="n">
-        <v>0.05458447802197802</v>
-      </c>
-      <c r="K231" t="n">
-        <v>0.2839571886446886</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>PTO_LA0</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>10</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>StartLowAndChangesToHigh</t>
-        </is>
-      </c>
-      <c r="F232" t="n">
-        <v>32</v>
-      </c>
-      <c r="G232" t="n">
-        <v>0.3463541666666666</v>
-      </c>
-      <c r="H232" t="n">
-        <v>0.3845756954122194</v>
-      </c>
-      <c r="I232" t="n">
-        <v>0.06798402052637813</v>
-      </c>
-      <c r="J232" t="n">
-        <v>0.1402310924369748</v>
-      </c>
-      <c r="K232" t="n">
-        <v>0.2061230742296918</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>PTO_LA0</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>10</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F233" t="n">
-        <v>32</v>
-      </c>
-      <c r="G233" t="n">
-        <v>0</v>
-      </c>
-      <c r="H233" t="n">
-        <v>0</v>
-      </c>
-      <c r="I233" t="n">
-        <v>0</v>
-      </c>
-      <c r="J233" t="n">
-        <v>0.03125</v>
-      </c>
-      <c r="K233" t="n">
-        <v>-0.03125</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>PTO_LA0</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>10</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F234" t="n">
-        <v>32</v>
-      </c>
-      <c r="G234" t="n">
-        <v>0.3385416666666666</v>
-      </c>
-      <c r="H234" t="n">
-        <v>0.3477639143777991</v>
-      </c>
-      <c r="I234" t="n">
-        <v>0.0614765555271299</v>
-      </c>
-      <c r="J234" t="n">
-        <v>0.05458447802197802</v>
-      </c>
-      <c r="K234" t="n">
-        <v>0.2839571886446886</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>PTO_LA0</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>10</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>StartLowAndChangesToHigh</t>
-        </is>
-      </c>
-      <c r="F235" t="n">
-        <v>32</v>
-      </c>
-      <c r="G235" t="n">
-        <v>0.3463541666666666</v>
-      </c>
-      <c r="H235" t="n">
-        <v>0.3845756954122194</v>
-      </c>
-      <c r="I235" t="n">
-        <v>0.06798402052637813</v>
-      </c>
-      <c r="J235" t="n">
-        <v>0.1402310924369748</v>
-      </c>
-      <c r="K235" t="n">
-        <v>0.2061230742296918</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>10</v>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F236" t="n">
-        <v>32</v>
-      </c>
-      <c r="G236" t="n">
-        <v>0.1796875</v>
-      </c>
-      <c r="H236" t="n">
-        <v>0.3365831998897578</v>
-      </c>
-      <c r="I236" t="n">
-        <v>0.05950006576887874</v>
-      </c>
-      <c r="J236" t="n">
-        <v>0.007612179487179484</v>
-      </c>
-      <c r="K236" t="n">
-        <v>0.1720753205128205</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>10</v>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F237" t="n">
-        <v>32</v>
-      </c>
-      <c r="G237" t="n">
-        <v>0.4171874999999999</v>
-      </c>
-      <c r="H237" t="n">
-        <v>0.4142939836979477</v>
-      </c>
-      <c r="I237" t="n">
-        <v>0.07323752131940195</v>
-      </c>
-      <c r="J237" t="n">
-        <v>0.07254464285714285</v>
-      </c>
-      <c r="K237" t="n">
-        <v>0.3446428571428571</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>10</v>
-      </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>StartLowAndChangesToHigh</t>
-        </is>
-      </c>
-      <c r="F238" t="n">
-        <v>32</v>
-      </c>
-      <c r="G238" t="n">
-        <v>0.4172281711344211</v>
-      </c>
-      <c r="H238" t="n">
-        <v>0.440570749941942</v>
-      </c>
-      <c r="I238" t="n">
-        <v>0.07788264121909748</v>
-      </c>
-      <c r="J238" t="n">
-        <v>0.1561710858585859</v>
-      </c>
-      <c r="K238" t="n">
-        <v>0.2610570852758353</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>10</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F239" t="n">
-        <v>32</v>
-      </c>
-      <c r="G239" t="n">
-        <v>0.1796875</v>
-      </c>
-      <c r="H239" t="n">
-        <v>0.3365831998897578</v>
-      </c>
-      <c r="I239" t="n">
-        <v>0.05950006576887874</v>
-      </c>
-      <c r="J239" t="n">
-        <v>0.007612179487179484</v>
-      </c>
-      <c r="K239" t="n">
-        <v>0.1720753205128205</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>10</v>
-      </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F240" t="n">
-        <v>32</v>
-      </c>
-      <c r="G240" t="n">
-        <v>0.4171874999999999</v>
-      </c>
-      <c r="H240" t="n">
-        <v>0.4142939836979477</v>
-      </c>
-      <c r="I240" t="n">
-        <v>0.07323752131940195</v>
-      </c>
-      <c r="J240" t="n">
-        <v>0.07254464285714285</v>
-      </c>
-      <c r="K240" t="n">
-        <v>0.3446428571428571</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>10</v>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>StartLowAndChangesToHigh</t>
-        </is>
-      </c>
-      <c r="F241" t="n">
-        <v>32</v>
-      </c>
-      <c r="G241" t="n">
-        <v>0.4172281711344211</v>
-      </c>
-      <c r="H241" t="n">
-        <v>0.440570749941942</v>
-      </c>
-      <c r="I241" t="n">
-        <v>0.07788264121909748</v>
-      </c>
-      <c r="J241" t="n">
-        <v>0.1561710858585859</v>
-      </c>
-      <c r="K241" t="n">
-        <v>0.2610570852758353</v>
       </c>
     </row>
   </sheetData>
@@ -10805,7 +9773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17057,694 +16025,6 @@
         <v>1.117647058823529</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>GRPO_LA0</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Obesity</t>
-        </is>
-      </c>
-      <c r="F146" t="n">
-        <v>48</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0.1076388888888889</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0.2436900701214716</v>
-      </c>
-      <c r="I146" t="n">
-        <v>0.0351736318958676</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0.05765467171717172</v>
-      </c>
-      <c r="K146" t="n">
-        <v>0.04998421717171716</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>GRPO_LA0</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Smoking</t>
-        </is>
-      </c>
-      <c r="F147" t="n">
-        <v>48</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0.1354166666666667</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0.2869424905931525</v>
-      </c>
-      <c r="I147" t="n">
-        <v>0.04141658104647457</v>
-      </c>
-      <c r="J147" t="n">
-        <v>0.04305555555555555</v>
-      </c>
-      <c r="K147" t="n">
-        <v>0.09236111111111112</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>GRPO_LA0</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>8</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Obesity</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>48</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0.08637152777777778</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0.2265929616284556</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0.03270587684816585</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0.05765467171717172</v>
-      </c>
-      <c r="K148" t="n">
-        <v>0.02871685606060605</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>GRPO_LA0</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>8</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Smoking</t>
-        </is>
-      </c>
-      <c r="F149" t="n">
-        <v>48</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0.1354166666666667</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0.2869424905931525</v>
-      </c>
-      <c r="I149" t="n">
-        <v>0.04141658104647457</v>
-      </c>
-      <c r="J149" t="n">
-        <v>0.04305555555555555</v>
-      </c>
-      <c r="K149" t="n">
-        <v>0.09236111111111112</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>GRPO_LA5</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Obesity</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>48</v>
-      </c>
-      <c r="G150" t="n">
-        <v>0.5461115681703917</v>
-      </c>
-      <c r="H150" t="n">
-        <v>0.4203785072367995</v>
-      </c>
-      <c r="I150" t="n">
-        <v>0.06067641107867481</v>
-      </c>
-      <c r="J150" t="n">
-        <v>0.0486111111111111</v>
-      </c>
-      <c r="K150" t="n">
-        <v>0.4975004570592806</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>GRPO_LA5</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Smoking</t>
-        </is>
-      </c>
-      <c r="F151" t="n">
-        <v>48</v>
-      </c>
-      <c r="G151" t="n">
-        <v>0.6431021524771525</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0.3917946805236284</v>
-      </c>
-      <c r="I151" t="n">
-        <v>0.05655069106684508</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0.1309027777777778</v>
-      </c>
-      <c r="K151" t="n">
-        <v>0.5121993746993747</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>GRPO_LA5</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Obesity</t>
-        </is>
-      </c>
-      <c r="F152" t="n">
-        <v>48</v>
-      </c>
-      <c r="G152" t="n">
-        <v>0.5461115681703917</v>
-      </c>
-      <c r="H152" t="n">
-        <v>0.4203785072367995</v>
-      </c>
-      <c r="I152" t="n">
-        <v>0.06067641107867481</v>
-      </c>
-      <c r="J152" t="n">
-        <v>0.0486111111111111</v>
-      </c>
-      <c r="K152" t="n">
-        <v>0.4975004570592806</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>GRPO_LA5</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Smoking</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>48</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0.6431021524771525</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0.3917946805236284</v>
-      </c>
-      <c r="I153" t="n">
-        <v>0.05655069106684508</v>
-      </c>
-      <c r="J153" t="n">
-        <v>0.1309027777777778</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0.5121993746993747</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>PTO_LA0</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Obesity</t>
-        </is>
-      </c>
-      <c r="F154" t="n">
-        <v>48</v>
-      </c>
-      <c r="G154" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0.3374450893660678</v>
-      </c>
-      <c r="I154" t="n">
-        <v>0.04870600329555414</v>
-      </c>
-      <c r="J154" t="n">
-        <v>0.06026785714285714</v>
-      </c>
-      <c r="K154" t="n">
-        <v>0.1619543650793651</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>PTO_LA0</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Smoking</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>48</v>
-      </c>
-      <c r="G155" t="n">
-        <v>0.234375</v>
-      </c>
-      <c r="H155" t="n">
-        <v>0.3415028365215227</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0.04929168864868048</v>
-      </c>
-      <c r="J155" t="n">
-        <v>0.0904425231631114</v>
-      </c>
-      <c r="K155" t="n">
-        <v>0.1439324768368886</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>PTO_LA0</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Obesity</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>48</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="H156" t="n">
-        <v>0.3374450893660678</v>
-      </c>
-      <c r="I156" t="n">
-        <v>0.04870600329555414</v>
-      </c>
-      <c r="J156" t="n">
-        <v>0.06026785714285714</v>
-      </c>
-      <c r="K156" t="n">
-        <v>0.1619543650793651</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>PTO_LA0</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Smoking</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>48</v>
-      </c>
-      <c r="G157" t="n">
-        <v>0.234375</v>
-      </c>
-      <c r="H157" t="n">
-        <v>0.3415028365215227</v>
-      </c>
-      <c r="I157" t="n">
-        <v>0.04929168864868048</v>
-      </c>
-      <c r="J157" t="n">
-        <v>0.0904425231631114</v>
-      </c>
-      <c r="K157" t="n">
-        <v>0.1439324768368886</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Obesity</t>
-        </is>
-      </c>
-      <c r="F158" t="n">
-        <v>48</v>
-      </c>
-      <c r="G158" t="n">
-        <v>0.2849492521367521</v>
-      </c>
-      <c r="H158" t="n">
-        <v>0.3734680729129244</v>
-      </c>
-      <c r="I158" t="n">
-        <v>0.05390547310750192</v>
-      </c>
-      <c r="J158" t="n">
-        <v>0.08229166666666667</v>
-      </c>
-      <c r="K158" t="n">
-        <v>0.2026575854700854</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>final</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Smoking</t>
-        </is>
-      </c>
-      <c r="F159" t="n">
-        <v>48</v>
-      </c>
-      <c r="G159" t="n">
-        <v>0.3911195286195286</v>
-      </c>
-      <c r="H159" t="n">
-        <v>0.4430903101067879</v>
-      </c>
-      <c r="I159" t="n">
-        <v>0.06395457745386719</v>
-      </c>
-      <c r="J159" t="n">
-        <v>0.07526027213527213</v>
-      </c>
-      <c r="K159" t="n">
-        <v>0.3158592564842564</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Obesity</t>
-        </is>
-      </c>
-      <c r="F160" t="n">
-        <v>48</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0.2849492521367521</v>
-      </c>
-      <c r="H160" t="n">
-        <v>0.3734680729129244</v>
-      </c>
-      <c r="I160" t="n">
-        <v>0.05390547310750192</v>
-      </c>
-      <c r="J160" t="n">
-        <v>0.08229166666666667</v>
-      </c>
-      <c r="K160" t="n">
-        <v>0.2026575854700854</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>MIPROC</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>best</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>PTO_LA5</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Smoking</t>
-        </is>
-      </c>
-      <c r="F161" t="n">
-        <v>48</v>
-      </c>
-      <c r="G161" t="n">
-        <v>0.3911195286195286</v>
-      </c>
-      <c r="H161" t="n">
-        <v>0.4430903101067879</v>
-      </c>
-      <c r="I161" t="n">
-        <v>0.06395457745386719</v>
-      </c>
-      <c r="J161" t="n">
-        <v>0.07526027213527213</v>
-      </c>
-      <c r="K161" t="n">
-        <v>0.3158592564842564</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
